--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_0BCF5AF934F2A37D1C4CD777FD1AB69042FCD0F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{333C2C5B-1071-446B-ABF9-8AB1676357A0}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_0BCF5AF934F2A37D1C4CD777FD1AB69042FCD0F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1AAE97-4BA1-4D7D-9FD4-BC020B327706}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'BRAM RIO'!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'BRAM SPIRIT'!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'BRAM TITAN'!$A$1:$S$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$F$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">posicoes!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2610,7 +2610,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_ED2C76715DE457A10B18CCCFA94F210CDCB26DEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAEB9092-A730-4D50-A45F-1F96B04BF432}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_ED2C76715DE457A10B18CCCFA94F210CDCB26DEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1DA627C-664B-4C47-95FA-82E5A1CA002E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="posicoes" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BRAM ATLAS'!$A$1:$S$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BRAM BAHIA'!$A$1:$S$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BRAM BAHIA'!$A$1:$S$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BRAM BELEM'!$A$1:$S$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BRAM BRASIL'!$A$1:$S$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRAM BRASILIA'!$A$1:$S$15</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="170">
   <si>
     <t>unidade</t>
   </si>
@@ -555,9 +555,6 @@
     <t>na</t>
   </si>
   <si>
-    <t>underway using engine</t>
-  </si>
-  <si>
     <t>ACTIVE</t>
   </si>
   <si>
@@ -570,25 +567,13 @@
     <t>Stopped</t>
   </si>
   <si>
-    <t>Underway using engine</t>
-  </si>
-  <si>
     <t>Moored</t>
   </si>
   <si>
-    <t>stopped</t>
-  </si>
-  <si>
     <t>At Anchor</t>
   </si>
   <si>
-    <t>restricted manoeuvrability</t>
-  </si>
-  <si>
-    <t>moored</t>
-  </si>
-  <si>
-    <t>at anchor</t>
+    <t>At anchor</t>
   </si>
 </sst>
 </file>
@@ -2624,6 +2609,7 @@
     <col min="9" max="9" width="2.6640625" customWidth="1"/>
     <col min="10" max="10" width="2.109375" customWidth="1"/>
     <col min="17" max="17" width="21.77734375" customWidth="1"/>
+    <col min="19" max="19" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -2741,7 +2727,7 @@
         <v>0.83680555555555558</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -2770,7 +2756,7 @@
         <v>0.63194444444444442</v>
       </c>
       <c r="S3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -2799,7 +2785,7 @@
         <v>0.2326388888888889</v>
       </c>
       <c r="S4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -2822,7 +2808,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -2845,7 +2831,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -2868,7 +2854,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -2891,7 +2877,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -2908,7 +2894,7 @@
         <v>46226.897222222222</v>
       </c>
       <c r="S9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -2925,7 +2911,7 @@
         <v>46227.286805555559</v>
       </c>
       <c r="S10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -2942,7 +2928,7 @@
         <v>46227.882638888892</v>
       </c>
       <c r="S11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -2959,7 +2945,7 @@
         <v>46228.268055555563</v>
       </c>
       <c r="S12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -2976,7 +2962,7 @@
         <v>46229.375</v>
       </c>
       <c r="S13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -2993,7 +2979,7 @@
         <v>46230.347916666673</v>
       </c>
       <c r="S14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -3010,7 +2996,7 @@
         <v>46230.85833333333</v>
       </c>
       <c r="S15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -3027,7 +3013,7 @@
         <v>46231.341666666667</v>
       </c>
       <c r="S16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3046,6 +3032,7 @@
     <col min="6" max="6" width="3.5546875" customWidth="1"/>
     <col min="7" max="7" width="5.21875" customWidth="1"/>
     <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -3133,7 +3120,7 @@
         <v>0.76875000000000004</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -3162,7 +3149,7 @@
         <v>0.23125000000000001</v>
       </c>
       <c r="S3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -3185,7 +3172,7 @@
         <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -3208,7 +3195,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -3231,7 +3218,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -3254,7 +3241,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -3271,7 +3258,7 @@
         <v>46226.143055555563</v>
       </c>
       <c r="S8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -3288,7 +3275,7 @@
         <v>46227.281944444447</v>
       </c>
       <c r="S9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -3305,7 +3292,7 @@
         <v>46227.468055555553</v>
       </c>
       <c r="S10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -3322,7 +3309,7 @@
         <v>46227.468055555553</v>
       </c>
       <c r="S11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -3339,7 +3326,7 @@
         <v>46229.375</v>
       </c>
       <c r="S12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -3356,7 +3343,7 @@
         <v>46230.352083333331</v>
       </c>
       <c r="S13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -3373,7 +3360,7 @@
         <v>46230.859027777777</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -3390,7 +3377,7 @@
         <v>46231.330555555563</v>
       </c>
       <c r="S15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -3408,6 +3395,7 @@
     <col min="5" max="5" width="6.109375" customWidth="1"/>
     <col min="6" max="6" width="5.21875" customWidth="1"/>
     <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -3495,7 +3483,7 @@
         <v>0.49375000000000002</v>
       </c>
       <c r="S2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -3524,7 +3512,7 @@
         <v>0.26458333333333328</v>
       </c>
       <c r="S3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -3547,7 +3535,7 @@
         <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -3570,7 +3558,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -3593,7 +3581,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -3616,7 +3604,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -3633,7 +3621,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -3650,7 +3638,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -3667,7 +3655,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -3684,7 +3672,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -3701,7 +3689,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -3718,7 +3706,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -3735,7 +3723,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -3752,7 +3740,7 @@
         <v>46226.459027777782</v>
       </c>
       <c r="S15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3889,7 +3877,7 @@
         <v>0.81944444444444442</v>
       </c>
       <c r="S2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -3918,7 +3906,7 @@
         <v>0.82361111111111107</v>
       </c>
       <c r="S3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -3947,7 +3935,7 @@
         <v>0.67152777777777772</v>
       </c>
       <c r="S4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -3970,7 +3958,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -3993,7 +3981,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -4016,7 +4004,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -4039,7 +4027,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -4056,7 +4044,7 @@
         <v>46226.445833333331</v>
       </c>
       <c r="S9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -4073,7 +4061,7 @@
         <v>46226.445833333331</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -4090,7 +4078,7 @@
         <v>46226.445833333331</v>
       </c>
       <c r="S11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -4107,7 +4095,7 @@
         <v>46227.974305555559</v>
       </c>
       <c r="S12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -4124,7 +4112,7 @@
         <v>46229.370138888888</v>
       </c>
       <c r="S13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -4141,7 +4129,7 @@
         <v>46230.356944444437</v>
       </c>
       <c r="S14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -4158,7 +4146,7 @@
         <v>46230.854861111111</v>
       </c>
       <c r="S15" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -4175,7 +4163,7 @@
         <v>46231.350694444453</v>
       </c>
       <c r="S16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -4282,7 +4270,7 @@
         <v>0.21875</v>
       </c>
       <c r="S2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -4311,7 +4299,7 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="S3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -4334,7 +4322,7 @@
         <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -4357,7 +4345,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -4380,7 +4368,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -4403,7 +4391,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -4420,7 +4408,7 @@
         <v>46226.421527777777</v>
       </c>
       <c r="S8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -4437,7 +4425,7 @@
         <v>46226.421527777777</v>
       </c>
       <c r="S9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -4454,7 +4442,7 @@
         <v>46226.421527777777</v>
       </c>
       <c r="S10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -4471,7 +4459,7 @@
         <v>46226.421527777777</v>
       </c>
       <c r="S11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -4488,7 +4476,7 @@
         <v>46226.421527777777</v>
       </c>
       <c r="S12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -4505,7 +4493,7 @@
         <v>46230.306944444441</v>
       </c>
       <c r="S13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -4522,7 +4510,7 @@
         <v>46230.361111111109</v>
       </c>
       <c r="S14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -4539,7 +4527,7 @@
         <v>46231.151388888888</v>
       </c>
       <c r="S15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -4677,7 +4665,7 @@
         <v>0.76388888888888884</v>
       </c>
       <c r="S2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -4706,7 +4694,7 @@
         <v>0.76388888888888884</v>
       </c>
       <c r="S3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -4735,7 +4723,7 @@
         <v>0.22013888888888891</v>
       </c>
       <c r="S4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -4758,7 +4746,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -4781,7 +4769,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -4804,7 +4792,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -4827,7 +4815,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -4844,7 +4832,7 @@
         <v>46226.880555555559</v>
       </c>
       <c r="S9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -4861,7 +4849,7 @@
         <v>46227.27847222222</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -4878,7 +4866,7 @@
         <v>46227.334722222222</v>
       </c>
       <c r="S11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -4895,7 +4883,7 @@
         <v>46227.334722222222</v>
       </c>
       <c r="S12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -4912,7 +4900,7 @@
         <v>46227.334722222222</v>
       </c>
       <c r="S13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -4929,7 +4917,7 @@
         <v>46230.101388888892</v>
       </c>
       <c r="S14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -4946,7 +4934,7 @@
         <v>46230.708333333343</v>
       </c>
       <c r="S15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -4963,7 +4951,7 @@
         <v>46231.306250000001</v>
       </c>
       <c r="S16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4980,6 +4968,7 @@
     <col min="1" max="1" width="30.109375" style="11" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="17" max="17" width="20.77734375" style="11" customWidth="1"/>
+    <col min="19" max="19" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -5097,7 +5086,7 @@
         <v>0.86111111111111116</v>
       </c>
       <c r="S2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -5126,7 +5115,7 @@
         <v>0.26180555555555562</v>
       </c>
       <c r="S3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -5155,7 +5144,7 @@
         <v>0.23125000000000001</v>
       </c>
       <c r="S4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -5178,7 +5167,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -5201,7 +5190,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -5224,7 +5213,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -5247,7 +5236,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -5264,7 +5253,7 @@
         <v>46226.480555555558</v>
       </c>
       <c r="S9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -5281,7 +5270,7 @@
         <v>46226.480555555558</v>
       </c>
       <c r="S10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -5298,7 +5287,7 @@
         <v>46226.480555555558</v>
       </c>
       <c r="S11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -5315,7 +5304,7 @@
         <v>46226.480555555558</v>
       </c>
       <c r="S12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -5332,7 +5321,7 @@
         <v>46226.480555555558</v>
       </c>
       <c r="S13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -5349,7 +5338,7 @@
         <v>46230.34652777778</v>
       </c>
       <c r="S14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -5366,7 +5355,7 @@
         <v>46230.85833333333</v>
       </c>
       <c r="S15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -5383,7 +5372,7 @@
         <v>46231.342361111107</v>
       </c>
       <c r="S16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -5394,7 +5383,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5409,6 +5397,7 @@
     <col min="11" max="11" width="7.21875" customWidth="1"/>
     <col min="12" max="12" width="7" customWidth="1"/>
     <col min="17" max="17" width="29.88671875" style="11" customWidth="1"/>
+    <col min="19" max="19" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -5526,10 +5515,10 @@
         <v>0.79583333333333328</v>
       </c>
       <c r="S2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>46224.231249999997</v>
       </c>
@@ -5555,7 +5544,7 @@
         <v>0.5541666666666667</v>
       </c>
       <c r="S3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -5578,10 +5567,10 @@
         <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>46225.229166666657</v>
       </c>
@@ -5601,10 +5590,10 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>46225.859027777777</v>
       </c>
@@ -5624,7 +5613,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -5647,10 +5636,10 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>46226.9</v>
       </c>
@@ -5664,7 +5653,7 @@
         <v>46226.897916666669</v>
       </c>
       <c r="S8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -5681,7 +5670,7 @@
         <v>46227.287499999999</v>
       </c>
       <c r="S9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -5698,7 +5687,7 @@
         <v>46227.379861111112</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -5715,10 +5704,10 @@
         <v>46228.011805555558</v>
       </c>
       <c r="S11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>46229.378472222219</v>
       </c>
@@ -5732,10 +5721,10 @@
         <v>46228.867361111108</v>
       </c>
       <c r="S12" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>46230.353472222218</v>
       </c>
@@ -5749,7 +5738,7 @@
         <v>46228.867361111108</v>
       </c>
       <c r="S13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -5766,7 +5755,7 @@
         <v>46230.787499999999</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -5783,17 +5772,11 @@
         <v>46230.964583333327</v>
       </c>
       <c r="S15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S14" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="18">
-      <filters>
-        <filter val="Underway using engine"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S15" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5809,6 +5792,7 @@
     <col min="9" max="9" width="3.5546875" customWidth="1"/>
     <col min="10" max="10" width="4.44140625" customWidth="1"/>
     <col min="17" max="17" width="34.44140625" style="11" customWidth="1"/>
+    <col min="19" max="19" width="37.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -5926,7 +5910,7 @@
         <v>0.84513888888888888</v>
       </c>
       <c r="S2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -5955,7 +5939,7 @@
         <v>0.63194444444444442</v>
       </c>
       <c r="S3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -5984,7 +5968,7 @@
         <v>0.74861111111111112</v>
       </c>
       <c r="S4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -6007,7 +5991,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -6030,7 +6014,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -6053,7 +6037,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -6076,7 +6060,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -6093,7 +6077,7 @@
         <v>46226.369444444441</v>
       </c>
       <c r="S9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -6110,7 +6094,7 @@
         <v>46226.369444444441</v>
       </c>
       <c r="S10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -6127,7 +6111,7 @@
         <v>46226.369444444441</v>
       </c>
       <c r="S11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -6144,7 +6128,7 @@
         <v>46226.369444444441</v>
       </c>
       <c r="S12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -6161,7 +6145,7 @@
         <v>46229.372916666667</v>
       </c>
       <c r="S13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -6178,7 +6162,7 @@
         <v>46230.351388888892</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -6195,7 +6179,7 @@
         <v>46230.856944444437</v>
       </c>
       <c r="S15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -6212,7 +6196,7 @@
         <v>46231.342361111107</v>
       </c>
       <c r="S16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -6360,7 +6344,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="S2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -6393,7 +6377,7 @@
         <v>0.63124999999999998</v>
       </c>
       <c r="S3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -6426,7 +6410,7 @@
         <v>0.38333333333333341</v>
       </c>
       <c r="S4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -6449,7 +6433,7 @@
         <v>0.73819444444444449</v>
       </c>
       <c r="S5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -6472,7 +6456,7 @@
         <v>0.23125000000000001</v>
       </c>
       <c r="S6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -6495,7 +6479,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -6518,7 +6502,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -6541,7 +6525,7 @@
         <v>162</v>
       </c>
       <c r="S9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -6564,7 +6548,7 @@
         <v>162</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -6581,7 +6565,7 @@
         <v>46226.887499999997</v>
       </c>
       <c r="S11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -6598,7 +6582,7 @@
         <v>46227.26666666667</v>
       </c>
       <c r="S12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -6615,7 +6599,7 @@
         <v>46227.804166666669</v>
       </c>
       <c r="S13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -6632,7 +6616,7 @@
         <v>46227.804166666669</v>
       </c>
       <c r="S14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -6649,7 +6633,7 @@
         <v>46229.259027777778</v>
       </c>
       <c r="S15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -6666,7 +6650,7 @@
         <v>46230.288194444453</v>
       </c>
       <c r="S16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.3">
@@ -6683,7 +6667,7 @@
         <v>46230.804861111108</v>
       </c>
       <c r="S17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
@@ -6700,7 +6684,7 @@
         <v>46231.34097222222</v>
       </c>
       <c r="S18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -6719,6 +6703,7 @@
     <col min="6" max="6" width="3.6640625" customWidth="1"/>
     <col min="7" max="7" width="4.6640625" customWidth="1"/>
     <col min="17" max="17" width="23.21875" style="11" customWidth="1"/>
+    <col min="19" max="19" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -6836,7 +6821,7 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="S2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -6865,7 +6850,7 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="S3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -6894,7 +6879,7 @@
         <v>0.2326388888888889</v>
       </c>
       <c r="S4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -6917,7 +6902,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -6940,7 +6925,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -6963,7 +6948,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -6986,7 +6971,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -7003,7 +6988,7 @@
         <v>46225.324305555558</v>
       </c>
       <c r="S9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -7020,7 +7005,7 @@
         <v>46225.324305555558</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -7037,7 +7022,7 @@
         <v>46225.324305555558</v>
       </c>
       <c r="S11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -7054,7 +7039,7 @@
         <v>46225.324305555558</v>
       </c>
       <c r="S12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -7071,7 +7056,7 @@
         <v>46225.324305555558</v>
       </c>
       <c r="S13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -7088,7 +7073,7 @@
         <v>46225.324305555558</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -7105,7 +7090,7 @@
         <v>46225.324305555558</v>
       </c>
       <c r="S15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -7122,7 +7107,7 @@
         <v>46231.331250000003</v>
       </c>
       <c r="S16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -7262,7 +7247,7 @@
         <v>0.63888888888888884</v>
       </c>
       <c r="S2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -7291,7 +7276,7 @@
         <v>0.57638888888888884</v>
       </c>
       <c r="S3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -7320,7 +7305,7 @@
         <v>0.2326388888888889</v>
       </c>
       <c r="S4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -7343,7 +7328,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -7366,7 +7351,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -7389,7 +7374,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -7412,7 +7397,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -7429,7 +7414,7 @@
         <v>46226.643750000003</v>
       </c>
       <c r="S9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -7446,7 +7431,7 @@
         <v>46226.643750000003</v>
       </c>
       <c r="S10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -7463,7 +7448,7 @@
         <v>46227.793055555558</v>
       </c>
       <c r="S11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -7480,7 +7465,7 @@
         <v>46227.978472222218</v>
       </c>
       <c r="S12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -7497,7 +7482,7 @@
         <v>46229.37222222222</v>
       </c>
       <c r="S13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -7514,7 +7499,7 @@
         <v>46230.281944444447</v>
       </c>
       <c r="S14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -7531,7 +7516,7 @@
         <v>46230.783333333333</v>
       </c>
       <c r="S15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -7548,7 +7533,7 @@
         <v>46231.043055555558</v>
       </c>
       <c r="S16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7685,7 +7670,7 @@
         <v>0.90208333333333335</v>
       </c>
       <c r="S2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -7714,7 +7699,7 @@
         <v>0.64444444444444449</v>
       </c>
       <c r="S3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -7743,7 +7728,7 @@
         <v>0.71666666666666667</v>
       </c>
       <c r="S4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -7766,7 +7751,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -7789,7 +7774,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -7812,7 +7797,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -7835,7 +7820,7 @@
         <v>162</v>
       </c>
       <c r="S8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -7852,7 +7837,7 @@
         <v>46226.438194444447</v>
       </c>
       <c r="S9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -7869,7 +7854,7 @@
         <v>46226.438194444447</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -7886,7 +7871,7 @@
         <v>46226.438194444447</v>
       </c>
       <c r="S11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -7903,7 +7888,7 @@
         <v>46226.438194444447</v>
       </c>
       <c r="S12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -7920,7 +7905,7 @@
         <v>46229.374305555553</v>
       </c>
       <c r="S13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -7937,7 +7922,7 @@
         <v>46230.292361111111</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -7954,7 +7939,7 @@
         <v>46230.666666666657</v>
       </c>
       <c r="S15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
@@ -7971,7 +7956,7 @@
         <v>46231.31527777778</v>
       </c>
       <c r="S16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7989,6 +7974,7 @@
     <col min="6" max="6" width="5.77734375" customWidth="1"/>
     <col min="7" max="7" width="6.44140625" customWidth="1"/>
     <col min="17" max="17" width="16.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -8076,7 +8062,7 @@
         <v>0.65138888888888891</v>
       </c>
       <c r="S2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -8105,7 +8091,7 @@
         <v>0.2305555555555556</v>
       </c>
       <c r="S3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
@@ -8128,7 +8114,7 @@
         <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -8151,7 +8137,7 @@
         <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
@@ -8174,7 +8160,7 @@
         <v>162</v>
       </c>
       <c r="S6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
@@ -8197,7 +8183,7 @@
         <v>162</v>
       </c>
       <c r="S7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -8214,7 +8200,7 @@
         <v>46226.427083333343</v>
       </c>
       <c r="S8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -8231,7 +8217,7 @@
         <v>46226.427083333343</v>
       </c>
       <c r="S9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
@@ -8248,7 +8234,7 @@
         <v>46226.427083333343</v>
       </c>
       <c r="S10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
@@ -8265,7 +8251,7 @@
         <v>46228.259027777778</v>
       </c>
       <c r="S11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -8282,7 +8268,7 @@
         <v>46229.375</v>
       </c>
       <c r="S12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -8299,7 +8285,7 @@
         <v>46230.351388888892</v>
       </c>
       <c r="S13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -8316,7 +8302,7 @@
         <v>46230.857638888891</v>
       </c>
       <c r="S14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -8333,7 +8319,7 @@
         <v>46231.34097222222</v>
       </c>
       <c r="S15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_ED2C76715DE457A10B18CCCFA94F210CDCB26DEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1DA627C-664B-4C47-95FA-82E5A1CA002E}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_ED2C76715DE457A10B18CCCFA94F210CDCB26DEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D4D9E2D-FECB-4E85-809D-FEC832D71A59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="4" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4546,7 +4546,7 @@
     <col min="6" max="7" width="4.21875" customWidth="1"/>
     <col min="8" max="8" width="3.5546875" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="17" max="17" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.6640625" customWidth="1"/>
     <col min="19" max="19" width="34.109375" customWidth="1"/>
   </cols>
   <sheetData>

--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -2777,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3321,9 +3321,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-22.872578</v>
       </c>
@@ -3333,10 +3330,32 @@
       <c r="Q18" s="15" t="n">
         <v>46232.29375</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="M19" t="n">
+        <v>-22.872562</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-43.126026</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46234.65416666667</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -3354,7 +3373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" customWidth="1" min="1" max="1"/>
@@ -3815,9 +3834,6 @@
       <c r="A17" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B17" t="n">
-        <v/>
-      </c>
       <c r="M17" t="n">
         <v>-25.657017</v>
       </c>
@@ -3827,12 +3843,34 @@
       <c r="Q17" s="15" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B18" t="n">
         <v/>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M18" t="n">
+        <v>-22.851009</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-43.150425</v>
+      </c>
+      <c r="Q18" s="15" t="n">
+        <v>46234.64861111111</v>
+      </c>
+      <c r="R18" t="n">
+        <v/>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" customWidth="1" min="1" max="1"/>
@@ -4308,9 +4346,6 @@
       <c r="A17" s="15" t="n">
         <v>46232.30416666667</v>
       </c>
-      <c r="B17" t="n">
-        <v/>
-      </c>
       <c r="M17" t="n">
         <v>-22.428282</v>
       </c>
@@ -4320,10 +4355,32 @@
       <c r="Q17" s="15" t="n">
         <v>46226.45902777778</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B18" t="n">
         <v/>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="M18" t="n">
+        <v>-22.428282</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-41.738838</v>
+      </c>
+      <c r="Q18" s="15" t="n">
+        <v>46226.45902777778</v>
+      </c>
+      <c r="R18" t="n">
+        <v/>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -4341,7 +4398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" min="1" max="1"/>
@@ -4883,9 +4940,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.30416666667</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-22.843269</v>
       </c>
@@ -4895,12 +4949,34 @@
       <c r="Q18" s="15" t="n">
         <v>46232.30069444444</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M19" t="n">
+        <v>-23.321667</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-42.959999</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46232.78472222222</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5377,9 +5453,6 @@
       <c r="A17" s="15" t="n">
         <v>46232.30416666667</v>
       </c>
-      <c r="B17" t="n">
-        <v/>
-      </c>
       <c r="M17" t="n">
         <v>-22.869379</v>
       </c>
@@ -5389,12 +5462,34 @@
       <c r="Q17" s="15" t="n">
         <v>46232.30069444444</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B18" t="n">
         <v/>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M18" t="n">
+        <v>-23.29213</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-43.0215</v>
+      </c>
+      <c r="Q18" s="15" t="n">
+        <v>46233.2125</v>
+      </c>
+      <c r="R18" t="n">
+        <v/>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.5546875" customWidth="1" min="1" max="1"/>
@@ -5953,9 +6048,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.30416666667</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-24.743824</v>
       </c>
@@ -5965,10 +6057,32 @@
       <c r="Q18" s="15" t="n">
         <v>46232.29583333333</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65277777778</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="M19" t="n">
+        <v>-24.742044</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-42.376553</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -5986,7 +6100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.109375" customWidth="1" style="11" min="1" max="1"/>
@@ -6526,9 +6640,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-22.847364</v>
       </c>
@@ -6538,12 +6649,34 @@
       <c r="Q18" s="15" t="n">
         <v>46232.29027777778</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M19" t="n">
+        <v>-23.551134</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-42.889713</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46233.70625</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.77734375" customWidth="1" style="11" min="1" max="1"/>
@@ -7076,9 +7209,6 @@
       <c r="A17" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B17" t="n">
-        <v/>
-      </c>
       <c r="M17" t="n">
         <v>-22.374588</v>
       </c>
@@ -7088,12 +7218,34 @@
       <c r="Q17" s="15" t="n">
         <v>46232.28888888889</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B18" t="n">
         <v/>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>At Anchor</t>
+      <c r="M18" t="n">
+        <v>-22.506702</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-40.092682</v>
+      </c>
+      <c r="Q18" s="15" t="n">
+        <v>46233.65694444445</v>
+      </c>
+      <c r="R18" t="n">
+        <v/>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="34.44140625" customWidth="1" style="11" min="1" max="1"/>
@@ -7652,9 +7804,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-25.225563</v>
       </c>
@@ -7664,12 +7813,34 @@
       <c r="Q18" s="15" t="n">
         <v>46232.25138888889</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M19" t="n">
+        <v>-24.952517</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-42.499733</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46232.57083333333</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.33203125" customWidth="1" style="11" min="1" max="1"/>
@@ -8296,9 +8467,6 @@
       <c r="A20" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-21.866814</v>
       </c>
@@ -8308,10 +8476,32 @@
       <c r="Q20" s="15" t="n">
         <v>46232.29444444444</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.384457</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-41.766888</v>
+      </c>
+      <c r="Q21" s="15" t="n">
+        <v>46234.65555555555</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -8329,7 +8519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -8871,9 +9061,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-22.860498</v>
       </c>
@@ -8883,12 +9070,34 @@
       <c r="Q18" s="15" t="n">
         <v>46232.29513888889</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M19" t="n">
+        <v>-23.069031</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-43.120152</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46234.61736111111</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -8904,7 +9113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.77734375" customWidth="1" style="11" min="1" max="1"/>
@@ -9449,9 +9658,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-21.263704</v>
       </c>
@@ -9461,10 +9667,32 @@
       <c r="Q18" s="15" t="n">
         <v>46232.08472222222</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="M19" t="n">
+        <v>-21.262182</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-40.043133</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46234.61666666667</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -9482,7 +9710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="21.33203125" customWidth="1" style="11" min="1" max="1"/>
@@ -10024,9 +10252,6 @@
       <c r="A18" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B18" t="n">
-        <v/>
-      </c>
       <c r="M18" t="n">
         <v>-24.75424</v>
       </c>
@@ -10036,12 +10261,34 @@
       <c r="Q18" s="15" t="n">
         <v>46232.19513888889</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Restricted Manoeuvrability</t>
+      <c r="M19" t="n">
+        <v>-24.225149</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-42.67873</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46234.64791666667</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="11" min="1" max="1"/>
@@ -10517,9 +10764,6 @@
       <c r="A17" s="15" t="n">
         <v>46232.29652777778</v>
       </c>
-      <c r="B17" t="n">
-        <v/>
-      </c>
       <c r="M17" t="n">
         <v>-24.191208</v>
       </c>
@@ -10529,10 +10773,32 @@
       <c r="Q17" s="15" t="n">
         <v>46232.28819444445</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>46234.65763888889</v>
+      </c>
+      <c r="B18" t="n">
         <v/>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="M18" t="n">
+        <v>-25.126089</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-43.074348</v>
+      </c>
+      <c r="Q18" s="15" t="n">
+        <v>46232.60069444445</v>
+      </c>
+      <c r="R18" t="n">
+        <v/>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>

--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="4" activeTab="14" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" tabRatio="1000" firstSheet="4" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posicoes" sheetId="1" state="visible" r:id="rId1"/>
@@ -539,13 +539,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G93"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.88671875" customWidth="1" min="1" max="1"/>
-    <col width="24.6640625" customWidth="1" min="4" max="4"/>
-    <col width="15.33203125" customWidth="1" min="5" max="5"/>
-    <col width="12.6640625" customWidth="1" min="6" max="6"/>
-    <col width="15.6640625" customWidth="1" min="7" max="7"/>
+    <col width="32.85546875" customWidth="1" min="1" max="1"/>
+    <col width="24.7109375" customWidth="1" min="4" max="4"/>
+    <col width="15.28515625" customWidth="1" min="5" max="5"/>
+    <col width="12.7109375" customWidth="1" min="6" max="6"/>
+    <col width="15.7109375" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2713,7 +2713,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
           <t>VERMELHO 1 (PVM-1)Fixa (Habitada)</t>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="28.8" customHeight="1">
+    <row r="92" ht="28.9" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
           <t>VERMELHO 3 (PVM-3)Fixa (Desabitada)</t>
@@ -2777,17 +2777,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.21875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="2.6640625" customWidth="1" min="6" max="6"/>
-    <col width="3.33203125" customWidth="1" min="7" max="7"/>
-    <col width="2.5546875" customWidth="1" min="8" max="8"/>
-    <col width="2.6640625" customWidth="1" min="9" max="9"/>
-    <col width="2.109375" customWidth="1" min="10" max="10"/>
-    <col width="21.77734375" customWidth="1" min="17" max="17"/>
-    <col width="16.21875" customWidth="1" min="19" max="19"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="2.7109375" customWidth="1" min="6" max="6"/>
+    <col width="3.28515625" customWidth="1" min="7" max="7"/>
+    <col width="2.5703125" customWidth="1" min="8" max="8"/>
+    <col width="2.7109375" customWidth="1" min="9" max="9"/>
+    <col width="2.140625" customWidth="1" min="10" max="10"/>
+    <col width="21.7109375" customWidth="1" min="17" max="17"/>
+    <col width="16.28515625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3299,7 +3299,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M17" t="n">
@@ -3308,7 +3308,7 @@
       <c r="N17" t="n">
         <v>-43.143181</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.91527777778</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M18" t="n">
@@ -3327,7 +3327,7 @@
       <c r="N18" t="n">
         <v>-43.126068</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.29375</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -3337,11 +3337,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-22.872562</v>
@@ -3349,15 +3346,37 @@
       <c r="N19" t="n">
         <v>-43.126026</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46234.65416666667</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Moored</t>
+      <c r="M20" t="n">
+        <v>-22.845222</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-43.136353</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46235.40416666667</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -3373,14 +3392,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5546875" customWidth="1" min="1" max="1"/>
-    <col width="4.6640625" customWidth="1" min="5" max="5"/>
-    <col width="3.5546875" customWidth="1" min="6" max="6"/>
-    <col width="5.21875" customWidth="1" min="7" max="7"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="10.5703125" customWidth="1" min="1" max="1"/>
+    <col width="4.7109375" customWidth="1" min="5" max="5"/>
+    <col width="3.5703125" customWidth="1" min="6" max="6"/>
+    <col width="5.28515625" customWidth="1" min="7" max="7"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" min="17" max="17"/>
     <col width="35" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -3812,7 +3831,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M16" t="n">
@@ -3821,7 +3840,7 @@
       <c r="N16" t="n">
         <v>-42.82122</v>
       </c>
-      <c r="Q16" s="15" t="n">
+      <c r="Q16" s="10" t="n">
         <v>46231.89375</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -3831,7 +3850,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M17" t="n">
@@ -3840,7 +3859,7 @@
       <c r="N17" t="n">
         <v>-42.859467</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46232.28888888889</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -3850,11 +3869,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B18" t="n">
-        <v/>
       </c>
       <c r="M18" t="n">
         <v>-22.851009</v>
@@ -3862,13 +3878,35 @@
       <c r="N18" t="n">
         <v>-43.150425</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46234.64861111111</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="M19" t="n">
+        <v>-22.851898</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-43.15062</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
@@ -3886,14 +3924,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5546875" customWidth="1" min="1" max="1"/>
-    <col width="6.109375" customWidth="1" min="5" max="5"/>
-    <col width="5.21875" customWidth="1" min="6" max="6"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="30.77734375" customWidth="1" min="19" max="19"/>
+    <col width="10.5703125" customWidth="1" min="1" max="1"/>
+    <col width="6.140625" customWidth="1" min="5" max="5"/>
+    <col width="5.28515625" customWidth="1" min="6" max="6"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="30.7109375" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4324,7 +4362,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="10" t="n">
         <v>46231.91597222222</v>
       </c>
       <c r="M16" t="n">
@@ -4333,7 +4371,7 @@
       <c r="N16" t="n">
         <v>-41.738838</v>
       </c>
-      <c r="Q16" s="15" t="n">
+      <c r="Q16" s="10" t="n">
         <v>46226.45902777778</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -4343,7 +4381,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46232.30416666667</v>
       </c>
       <c r="M17" t="n">
@@ -4352,7 +4390,7 @@
       <c r="N17" t="n">
         <v>-41.738838</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46226.45902777778</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -4362,11 +4400,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46234.65277777778</v>
-      </c>
-      <c r="B18" t="n">
-        <v/>
       </c>
       <c r="M18" t="n">
         <v>-22.428282</v>
@@ -4374,15 +4409,37 @@
       <c r="N18" t="n">
         <v>-41.738838</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46226.45902777778</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M19" t="n">
+        <v>-22.478701</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-40.104019</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46234.7875</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -4398,14 +4455,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.77734375" customWidth="1" min="1" max="1"/>
-    <col width="5.21875" customWidth="1" min="5" max="5"/>
-    <col width="4.77734375" customWidth="1" min="6" max="6"/>
-    <col width="4.6640625" customWidth="1" min="7" max="7"/>
-    <col width="11.21875" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" min="5" max="5"/>
+    <col width="4.7109375" customWidth="1" min="6" max="7"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="17" max="17"/>
     <col width="35" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -4918,7 +4974,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91597222222</v>
       </c>
       <c r="M17" t="n">
@@ -4927,7 +4983,7 @@
       <c r="N17" t="n">
         <v>-43.148327</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.91319444445</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -4937,7 +4993,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.30416666667</v>
       </c>
       <c r="M18" t="n">
@@ -4946,7 +5002,7 @@
       <c r="N18" t="n">
         <v>-43.148186</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.30069444444</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -4956,11 +5012,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65277777778</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-23.321667</v>
@@ -4968,13 +5021,35 @@
       <c r="N19" t="n">
         <v>-42.959999</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46232.78472222222</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-23.321667</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.959999</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46232.78472222222</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -4992,15 +5067,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="4.44140625" customWidth="1" min="5" max="5"/>
-    <col width="4.21875" customWidth="1" min="6" max="6"/>
-    <col width="4.109375" customWidth="1" min="7" max="7"/>
-    <col width="19.5546875" bestFit="1" customWidth="1" min="17" max="17"/>
-    <col width="33.109375" customWidth="1" min="19" max="19"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="4.42578125" customWidth="1" min="5" max="5"/>
+    <col width="4.28515625" customWidth="1" min="6" max="6"/>
+    <col width="4.140625" customWidth="1" min="7" max="7"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="33.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5431,7 +5506,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="10" t="n">
         <v>46231.91597222222</v>
       </c>
       <c r="M16" t="n">
@@ -5440,7 +5515,7 @@
       <c r="N16" t="n">
         <v>-42.858665</v>
       </c>
-      <c r="Q16" s="15" t="n">
+      <c r="Q16" s="10" t="n">
         <v>46231.91319444445</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -5450,7 +5525,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46232.30416666667</v>
       </c>
       <c r="M17" t="n">
@@ -5459,7 +5534,7 @@
       <c r="N17" t="n">
         <v>-43.212753</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46232.30069444444</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -5469,11 +5544,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46234.65277777778</v>
-      </c>
-      <c r="B18" t="n">
-        <v/>
       </c>
       <c r="M18" t="n">
         <v>-23.29213</v>
@@ -5481,13 +5553,35 @@
       <c r="N18" t="n">
         <v>-43.0215</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46233.2125</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="M19" t="n">
+        <v>-23.29213</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-43.0215</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46233.2125</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -5505,16 +5599,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.5546875" customWidth="1" min="1" max="1"/>
-    <col width="3.6640625" customWidth="1" min="5" max="5"/>
-    <col width="4.21875" customWidth="1" min="6" max="7"/>
-    <col width="3.5546875" customWidth="1" min="8" max="8"/>
+    <col width="24.5703125" customWidth="1" min="1" max="1"/>
+    <col width="3.7109375" customWidth="1" min="5" max="5"/>
+    <col width="4.28515625" customWidth="1" min="6" max="7"/>
+    <col width="3.5703125" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="23.6640625" customWidth="1" min="17" max="17"/>
-    <col width="34.109375" customWidth="1" min="19" max="19"/>
+    <col width="23.7109375" customWidth="1" min="17" max="17"/>
+    <col width="34.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6026,7 +6120,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91597222222</v>
       </c>
       <c r="M17" t="n">
@@ -6035,7 +6129,7 @@
       <c r="N17" t="n">
         <v>-42.375866</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.86944444444</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -6045,7 +6139,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.30416666667</v>
       </c>
       <c r="M18" t="n">
@@ -6054,7 +6148,7 @@
       <c r="N18" t="n">
         <v>-42.375687</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.29583333333</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -6064,11 +6158,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65277777778</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-24.742044</v>
@@ -6076,13 +6167,35 @@
       <c r="N19" t="n">
         <v>-42.376553</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46232.60555555556</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.42013888889</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-24.742044</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.376553</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46232.60555555556</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -6100,13 +6213,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.109375" customWidth="1" style="11" min="1" max="1"/>
+    <col width="30.140625" customWidth="1" style="11" min="1" max="1"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="20.77734375" customWidth="1" style="11" min="17" max="17"/>
-    <col width="33.5546875" customWidth="1" min="19" max="19"/>
+    <col width="20.7109375" customWidth="1" style="11" min="17" max="17"/>
+    <col width="33.5703125" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6618,7 +6731,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M17" t="n">
@@ -6627,7 +6740,7 @@
       <c r="N17" t="n">
         <v>-43.138699</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.91111111111</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -6637,7 +6750,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M18" t="n">
@@ -6646,7 +6759,7 @@
       <c r="N18" t="n">
         <v>-43.138481</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.29027777778</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -6656,11 +6769,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-23.551134</v>
@@ -6668,13 +6778,35 @@
       <c r="N19" t="n">
         <v>-42.889713</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46233.70625</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-23.551134</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.889713</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46233.70625</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -6692,21 +6824,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27.77734375" customWidth="1" style="11" min="1" max="1"/>
-    <col width="10.44140625" customWidth="1" min="2" max="2"/>
-    <col width="7.77734375" customWidth="1" min="4" max="5"/>
-    <col width="6.88671875" customWidth="1" min="6" max="6"/>
-    <col width="1.44140625" customWidth="1" min="7" max="7"/>
-    <col width="4.77734375" customWidth="1" min="8" max="8"/>
-    <col width="4.44140625" customWidth="1" min="9" max="9"/>
-    <col width="2.6640625" customWidth="1" min="10" max="10"/>
-    <col width="7.21875" customWidth="1" min="11" max="11"/>
+    <col width="27.7109375" customWidth="1" style="11" min="1" max="1"/>
+    <col width="10.42578125" customWidth="1" min="2" max="2"/>
+    <col width="7.7109375" customWidth="1" min="4" max="5"/>
+    <col width="6.85546875" customWidth="1" min="6" max="6"/>
+    <col width="1.42578125" customWidth="1" min="7" max="7"/>
+    <col width="4.7109375" customWidth="1" min="8" max="8"/>
+    <col width="4.42578125" customWidth="1" min="9" max="9"/>
+    <col width="2.7109375" customWidth="1" min="10" max="10"/>
+    <col width="7.28515625" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="29.88671875" customWidth="1" style="11" min="17" max="17"/>
-    <col width="31.109375" customWidth="1" min="19" max="19"/>
+    <col width="29.85546875" customWidth="1" style="11" min="17" max="17"/>
+    <col width="31.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7187,7 +7319,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M16" t="n">
@@ -7196,7 +7328,7 @@
       <c r="N16" t="n">
         <v>-41.739471</v>
       </c>
-      <c r="Q16" s="15" t="n">
+      <c r="Q16" s="10" t="n">
         <v>46231.84097222222</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -7206,7 +7338,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M17" t="n">
@@ -7215,7 +7347,7 @@
       <c r="N17" t="n">
         <v>-41.739559</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46232.28888888889</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -7225,11 +7357,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B18" t="n">
-        <v/>
       </c>
       <c r="M18" t="n">
         <v>-22.506702</v>
@@ -7237,15 +7366,37 @@
       <c r="N18" t="n">
         <v>-40.092682</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46233.65694444445</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M19" t="n">
+        <v>-22.52906</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-40.045006</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46234.7875</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -7261,16 +7412,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34.44140625" customWidth="1" style="11" min="1" max="1"/>
-    <col width="3.5546875" customWidth="1" min="7" max="7"/>
-    <col width="3.109375" customWidth="1" min="8" max="8"/>
-    <col width="3.5546875" customWidth="1" min="9" max="9"/>
-    <col width="4.44140625" customWidth="1" min="10" max="10"/>
-    <col width="34.44140625" customWidth="1" style="11" min="17" max="17"/>
-    <col width="37.5546875" customWidth="1" min="19" max="19"/>
+    <col width="34.42578125" customWidth="1" style="11" min="1" max="1"/>
+    <col width="3.5703125" customWidth="1" min="7" max="7"/>
+    <col width="3.140625" customWidth="1" min="8" max="8"/>
+    <col width="3.5703125" customWidth="1" min="9" max="9"/>
+    <col width="4.42578125" customWidth="1" min="10" max="10"/>
+    <col width="34.42578125" customWidth="1" style="11" min="17" max="17"/>
+    <col width="37.5703125" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7782,7 +7933,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M17" t="n">
@@ -7791,7 +7942,7 @@
       <c r="N17" t="n">
         <v>-42.919586</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.91458333333</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -7801,7 +7952,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M18" t="n">
@@ -7810,7 +7961,7 @@
       <c r="N18" t="n">
         <v>-42.720108</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.25138888889</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -7820,11 +7971,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-24.952517</v>
@@ -7832,13 +7980,35 @@
       <c r="N19" t="n">
         <v>-42.499733</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46232.57083333333</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-24.952517</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-42.499733</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46232.57083333333</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -7856,26 +8026,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25.33203125" customWidth="1" style="11" min="1" max="1"/>
-    <col width="16.109375" customWidth="1" min="2" max="2"/>
-    <col width="6.44140625" customWidth="1" style="4" min="3" max="3"/>
+    <col width="25.28515625" customWidth="1" style="11" min="1" max="1"/>
+    <col width="16.140625" customWidth="1" min="2" max="2"/>
+    <col width="6.42578125" customWidth="1" style="4" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="7.109375" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="3.44140625" customWidth="1" min="6" max="6"/>
-    <col width="4.21875" customWidth="1" min="7" max="7"/>
-    <col width="11.109375" customWidth="1" style="3" min="8" max="8"/>
-    <col width="4.109375" customWidth="1" min="9" max="9"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="3.42578125" customWidth="1" min="6" max="6"/>
+    <col width="4.28515625" customWidth="1" min="7" max="7"/>
+    <col width="11.140625" customWidth="1" style="3" min="8" max="8"/>
+    <col width="4.140625" customWidth="1" min="9" max="9"/>
     <col width="7" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="4.21875" customWidth="1" min="11" max="11"/>
-    <col width="3.6640625" customWidth="1" min="12" max="12"/>
-    <col width="10.6640625" bestFit="1" customWidth="1" min="13" max="14"/>
-    <col width="10.6640625" customWidth="1" min="15" max="16"/>
-    <col width="24.33203125" customWidth="1" style="12" min="17" max="17"/>
-    <col width="14.88671875" bestFit="1" customWidth="1" min="18" max="18"/>
-    <col width="36.44140625" customWidth="1" min="19" max="19"/>
+    <col width="4.28515625" customWidth="1" min="11" max="11"/>
+    <col width="3.7109375" customWidth="1" min="12" max="12"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="13" max="14"/>
+    <col width="10.7109375" customWidth="1" min="15" max="16"/>
+    <col width="24.28515625" customWidth="1" style="12" min="17" max="17"/>
+    <col width="14.85546875" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="36.42578125" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8445,7 +8615,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M19" t="n">
@@ -8454,7 +8624,7 @@
       <c r="N19" t="n">
         <v>-41.006161</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46231.91527777778</v>
       </c>
       <c r="S19" t="inlineStr">
@@ -8464,7 +8634,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M20" t="n">
@@ -8473,7 +8643,7 @@
       <c r="N20" t="n">
         <v>-41.015121</v>
       </c>
-      <c r="Q20" s="15" t="n">
+      <c r="Q20" s="10" t="n">
         <v>46232.29444444444</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -8483,11 +8653,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B21" t="n">
-        <v/>
       </c>
       <c r="M21" t="n">
         <v>-22.384457</v>
@@ -8495,13 +8662,35 @@
       <c r="N21" t="n">
         <v>-41.766888</v>
       </c>
-      <c r="Q21" s="15" t="n">
+      <c r="Q21" s="10" t="n">
         <v>46234.65555555555</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.384434</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-41.768688</v>
+      </c>
+      <c r="Q22" s="15" t="n">
+        <v>46235.40069444444</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -8519,15 +8708,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.21875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.21875" customWidth="1" min="5" max="5"/>
-    <col width="3.6640625" customWidth="1" min="6" max="6"/>
-    <col width="4.6640625" customWidth="1" min="7" max="7"/>
-    <col width="23.21875" customWidth="1" style="11" min="17" max="17"/>
-    <col width="28.33203125" customWidth="1" min="19" max="19"/>
+    <col width="23.28515625" customWidth="1" style="11" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" min="5" max="5"/>
+    <col width="3.7109375" customWidth="1" min="6" max="6"/>
+    <col width="4.7109375" customWidth="1" min="7" max="7"/>
+    <col width="23.28515625" customWidth="1" style="11" min="17" max="17"/>
+    <col width="28.28515625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9039,7 +9228,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M17" t="n">
@@ -9048,7 +9237,7 @@
       <c r="N17" t="n">
         <v>-43.212166</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.91597222222</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -9058,7 +9247,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M18" t="n">
@@ -9067,7 +9256,7 @@
       <c r="N18" t="n">
         <v>-43.183395</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.29513888889</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -9077,11 +9266,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-23.069031</v>
@@ -9089,13 +9275,35 @@
       <c r="N19" t="n">
         <v>-43.120152</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46234.61736111111</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-23.319584</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-43.045639</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46234.69166666667</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -9113,17 +9321,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.77734375" customWidth="1" style="11" min="1" max="1"/>
-    <col width="3.33203125" customWidth="1" min="5" max="5"/>
-    <col width="3.6640625" customWidth="1" min="6" max="6"/>
-    <col width="4.44140625" customWidth="1" min="7" max="7"/>
-    <col width="4.109375" customWidth="1" min="8" max="8"/>
-    <col width="4.21875" customWidth="1" min="9" max="9"/>
-    <col width="4.109375" customWidth="1" min="10" max="10"/>
-    <col width="19.88671875" customWidth="1" style="11" min="17" max="17"/>
+    <col width="23.7109375" customWidth="1" style="11" min="1" max="1"/>
+    <col width="3.28515625" customWidth="1" min="5" max="5"/>
+    <col width="3.7109375" customWidth="1" min="6" max="6"/>
+    <col width="4.42578125" customWidth="1" min="7" max="7"/>
+    <col width="4.140625" customWidth="1" min="8" max="8"/>
+    <col width="4.28515625" customWidth="1" min="9" max="9"/>
+    <col width="4.140625" customWidth="1" min="10" max="10"/>
+    <col width="19.85546875" customWidth="1" style="11" min="17" max="17"/>
     <col width="27" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -9636,7 +9844,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M17" t="n">
@@ -9645,7 +9853,7 @@
       <c r="N17" t="n">
         <v>-40.043674</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.78194444445</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -9655,7 +9863,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M18" t="n">
@@ -9664,7 +9872,7 @@
       <c r="N18" t="n">
         <v>-40.043285</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.08472222222</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -9674,11 +9882,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-21.262182</v>
@@ -9686,13 +9891,35 @@
       <c r="N19" t="n">
         <v>-40.043133</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46234.61666666667</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="M20" t="n">
+        <v>-21.261974</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-40.043221</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46234.67222222222</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -9710,15 +9937,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21.33203125" customWidth="1" style="11" min="1" max="1"/>
-    <col width="18.6640625" customWidth="1" min="2" max="2"/>
-    <col width="11.88671875" customWidth="1" min="13" max="13"/>
+    <col width="26.5703125" customWidth="1" style="11" min="1" max="1"/>
+    <col width="18.7109375" customWidth="1" min="2" max="2"/>
+    <col width="11.85546875" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="20.6640625" customWidth="1" style="11" min="17" max="17"/>
-    <col width="26.109375" customWidth="1" min="19" max="19"/>
+    <col width="20.7109375" customWidth="1" style="11" min="17" max="17"/>
+    <col width="26.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10230,7 +10457,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M17" t="n">
@@ -10239,7 +10466,7 @@
       <c r="N17" t="n">
         <v>-42.347614</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46231.91111111111</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -10249,7 +10476,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M18" t="n">
@@ -10258,7 +10485,7 @@
       <c r="N18" t="n">
         <v>-42.347164</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.19513888889</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -10268,11 +10495,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B19" t="n">
-        <v/>
       </c>
       <c r="M19" t="n">
         <v>-24.225149</v>
@@ -10280,15 +10504,37 @@
       <c r="N19" t="n">
         <v>-42.67873</v>
       </c>
-      <c r="Q19" s="15" t="n">
+      <c r="Q19" s="10" t="n">
         <v>46234.64791666667</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B20" t="n">
         <v/>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M20" t="n">
+        <v>-22.87258</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-43.125988</v>
+      </c>
+      <c r="Q20" s="15" t="n">
+        <v>46235.40347222222</v>
+      </c>
+      <c r="R20" t="n">
+        <v/>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -10304,14 +10550,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:S19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.77734375" customWidth="1" min="6" max="6"/>
-    <col width="6.44140625" customWidth="1" min="7" max="7"/>
-    <col width="16.5546875" bestFit="1" customWidth="1" style="11" min="17" max="17"/>
-    <col width="26.109375" customWidth="1" min="19" max="19"/>
+    <col width="5.7109375" customWidth="1" min="6" max="6"/>
+    <col width="6.42578125" customWidth="1" min="7" max="7"/>
+    <col width="16.5703125" bestFit="1" customWidth="1" style="11" min="17" max="17"/>
+    <col width="26.140625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10742,7 +10988,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="10" t="n">
         <v>46231.91805555556</v>
       </c>
       <c r="M16" t="n">
@@ -10751,7 +10997,7 @@
       <c r="N16" t="n">
         <v>-43.212711</v>
       </c>
-      <c r="Q16" s="15" t="n">
+      <c r="Q16" s="10" t="n">
         <v>46231.91180555556</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -10761,7 +11007,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="10" t="n">
         <v>46232.29652777778</v>
       </c>
       <c r="M17" t="n">
@@ -10770,7 +11016,7 @@
       <c r="N17" t="n">
         <v>-43.024834</v>
       </c>
-      <c r="Q17" s="15" t="n">
+      <c r="Q17" s="10" t="n">
         <v>46232.28819444445</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -10780,11 +11026,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="10" t="n">
         <v>46234.65763888889</v>
-      </c>
-      <c r="B18" t="n">
-        <v/>
       </c>
       <c r="M18" t="n">
         <v>-25.126089</v>
@@ -10792,13 +11035,35 @@
       <c r="N18" t="n">
         <v>-43.074348</v>
       </c>
-      <c r="Q18" s="15" t="n">
+      <c r="Q18" s="10" t="n">
         <v>46232.60069444445</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>46235.40555555555</v>
+      </c>
+      <c r="B19" t="n">
         <v/>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="M19" t="n">
+        <v>-25.126089</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-43.074348</v>
+      </c>
+      <c r="Q19" s="15" t="n">
+        <v>46232.60069444445</v>
+      </c>
+      <c r="R19" t="n">
+        <v/>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>

--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.140625" customWidth="1" style="8" min="1" max="1"/>
@@ -1103,9 +1103,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-24.745529</v>
       </c>
@@ -1115,10 +1112,32 @@
       <c r="Q21" s="12" t="n">
         <v>46236.2</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-24.744942</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.410927</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46236.99375</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -1136,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -1654,9 +1673,6 @@
       <c r="A20" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-24.174898</v>
       </c>
@@ -1666,10 +1682,32 @@
       <c r="Q20" s="12" t="n">
         <v>46236.34583333333</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-25.736458</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.902584</v>
+      </c>
+      <c r="Q21" s="12" t="n">
+        <v>46236.99722222222</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -1687,7 +1725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -2204,9 +2242,6 @@
       <c r="A20" s="12" t="n">
         <v>46236.34930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.478701</v>
       </c>
@@ -2216,10 +2251,32 @@
       <c r="Q20" s="12" t="n">
         <v>46234.7875</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="M21" t="n">
+        <v>-22.478701</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-40.104019</v>
+      </c>
+      <c r="Q21" s="12" t="n">
+        <v>46234.7875</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -2237,7 +2294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -2835,9 +2892,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.34930555556</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-24.606754</v>
       </c>
@@ -2847,12 +2901,34 @@
       <c r="Q21" s="12" t="n">
         <v>46236.27291666667</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M22" t="n">
+        <v>-24.628132</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.415447</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46236.93055555555</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3386,9 +3462,6 @@
       <c r="A20" s="12" t="n">
         <v>46236.34930555556</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-23.29213</v>
       </c>
@@ -3398,12 +3471,34 @@
       <c r="Q20" s="12" t="n">
         <v>46233.2125</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M21" t="n">
+        <v>-25.401537</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-42.725697</v>
+      </c>
+      <c r="Q21" s="12" t="n">
+        <v>46236.81041666667</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.5703125" customWidth="1" min="1" max="1"/>
@@ -4019,9 +4114,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.34930555556</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-24.742044</v>
       </c>
@@ -4031,10 +4123,32 @@
       <c r="Q21" s="12" t="n">
         <v>46232.60555555556</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-24.710625</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.371201</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46236.93541666667</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -4052,7 +4166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.7109375" customWidth="1" style="8" min="1" max="1"/>
@@ -4626,9 +4740,6 @@
       <c r="A20" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-22.239691</v>
       </c>
@@ -4638,12 +4749,34 @@
       <c r="Q20" s="12" t="n">
         <v>46235.69583333333</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Underway using Engine</t>
+      <c r="M21" t="n">
+        <v>-21.863884</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-41.016964</v>
+      </c>
+      <c r="Q21" s="12" t="n">
+        <v>46237.32986111111</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.42578125" customWidth="1" style="8" min="1" max="1"/>
@@ -5259,9 +5392,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-24.952517</v>
       </c>
@@ -5271,12 +5401,34 @@
       <c r="Q21" s="12" t="n">
         <v>46232.57083333333</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M22" t="n">
+        <v>-25.151657</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-42.81712</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46236.77361111111</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.28515625" customWidth="1" style="8" min="1" max="1"/>
@@ -5960,9 +6112,6 @@
       <c r="A23" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B23" t="n">
-        <v/>
-      </c>
       <c r="M23" t="n">
         <v>-22.039877</v>
       </c>
@@ -5972,10 +6121,32 @@
       <c r="Q23" s="12" t="n">
         <v>46236.32152777778</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B24" t="n">
         <v/>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="M24" t="n">
+        <v>-22.236013</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-39.991325</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46237.31875</v>
+      </c>
+      <c r="R24" t="n">
+        <v/>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Underway</t>
         </is>
@@ -5993,7 +6164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.28515625" customWidth="1" style="8" min="1" max="1"/>
@@ -6592,9 +6763,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-23.319584</v>
       </c>
@@ -6604,10 +6772,32 @@
       <c r="Q21" s="12" t="n">
         <v>46234.69166666667</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-23.319584</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.045639</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46234.69166666667</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -6625,7 +6815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.7109375" customWidth="1" style="8" min="1" max="1"/>
@@ -7227,9 +7417,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-21.251488</v>
       </c>
@@ -7239,10 +7426,32 @@
       <c r="Q21" s="12" t="n">
         <v>46236.22569444445</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-21.251385</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-40.018005</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46237.32569444444</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Restricted Manoeuvrability</t>
         </is>
@@ -7260,7 +7469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39.7109375" customWidth="1" style="8" min="1" max="1"/>
@@ -7859,9 +8068,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-22.872581</v>
       </c>
@@ -7871,10 +8077,32 @@
       <c r="Q21" s="12" t="n">
         <v>46236.35</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.87257</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.126041</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -7892,7 +8120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="8" min="1" max="1"/>
@@ -8409,9 +8637,6 @@
       <c r="A20" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B20" t="n">
-        <v/>
-      </c>
       <c r="M20" t="n">
         <v>-25.169064</v>
       </c>
@@ -8421,12 +8646,34 @@
       <c r="Q20" s="12" t="n">
         <v>46236.21944444445</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B21" t="n">
         <v/>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Stopped</t>
+      <c r="M21" t="n">
+        <v>-22.894571</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-43.212265</v>
+      </c>
+      <c r="Q21" s="12" t="n">
+        <v>46237.32777777778</v>
+      </c>
+      <c r="R21" t="n">
+        <v/>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -8442,7 +8689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9043,9 +9290,6 @@
       <c r="A21" s="12" t="n">
         <v>46236.35347222222</v>
       </c>
-      <c r="B21" t="n">
-        <v/>
-      </c>
       <c r="M21" t="n">
         <v>-22.844938</v>
       </c>
@@ -9055,10 +9299,32 @@
       <c r="Q21" s="12" t="n">
         <v>46236.34791666667</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="n">
+        <v>46237.33402777778</v>
+      </c>
+      <c r="B22" t="n">
         <v/>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="M22" t="n">
+        <v>-22.844833</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-43.13636</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>46237.32708333333</v>
+      </c>
+      <c r="R22" t="n">
+        <v/>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>At Anchor</t>
         </is>
